--- a/pds_admin_raj/Backend/Backend/Result_Sheet12.xlsx
+++ b/pds_admin_raj/Backend/Backend/Result_Sheet12.xlsx
@@ -1629,12 +1629,12 @@
     <t>PWS NEELKANTH WAEHOUSE HMH</t>
   </si>
   <si>
+    <t>PWS ABP AGRIWAREHOUSING HMO</t>
+  </si>
+  <si>
     <t>PWS PREETI ENTERPRISES HMO</t>
   </si>
   <si>
-    <t>PWS ABP AGRIWAREHOUSING HMO</t>
-  </si>
-  <si>
     <t xml:space="preserve">CWC BARAN </t>
   </si>
   <si>
@@ -1653,6 +1653,9 @@
     <t>PWS RAMDEV ENTERPRISES PILIBANGA</t>
   </si>
   <si>
+    <t>PWS RAJKUMARI PILIBANGA</t>
+  </si>
+  <si>
     <t>PWS AGGARWAL FOODS PILIBANGA</t>
   </si>
   <si>
@@ -1662,9 +1665,6 @@
     <t>PWS SUSHMA DEVI II PILIBANGA</t>
   </si>
   <si>
-    <t>PWS RAJKUMARI PILIBANGA</t>
-  </si>
-  <si>
     <t>PWS DARSHNA DEVI SANGARIA</t>
   </si>
   <si>
@@ -1854,15 +1854,15 @@
     <t>PWS REKHA DEVI JAITSAR</t>
   </si>
   <si>
+    <t>PWS RAJ WAREHOUSING JAITSAR</t>
+  </si>
+  <si>
+    <t>PWS MAMTA DEVI JAITSAR</t>
+  </si>
+  <si>
     <t>PWS MRG WAREHOUSE JAITSAR</t>
   </si>
   <si>
-    <t>PWS MAMTA DEVI JAITSAR</t>
-  </si>
-  <si>
-    <t>PWS RAJ WAREHOUSING JAITSAR</t>
-  </si>
-  <si>
     <t>PWS RELIABLE STATE SEEDS CORP KESRISINGHPUR</t>
   </si>
   <si>
@@ -1932,13 +1932,13 @@
     <t>PWS SUSHILA ARORA SURATGARH</t>
   </si>
   <si>
+    <t>PWS SHAKTI GRANARIES SURATGARH</t>
+  </si>
+  <si>
+    <t>PWS SANKHLA ENTERPRISES SURATGARH</t>
+  </si>
+  <si>
     <t>PWS SHAKTI GRAINRIES II SURATGARH</t>
-  </si>
-  <si>
-    <t>PWS SANKHLA ENTERPRISES SURATGARH</t>
-  </si>
-  <si>
-    <t>PWS SHAKTI GRANARIES SURATGARH</t>
   </si>
   <si>
     <t xml:space="preserve">RSWC BUNDI HATTIPURA UNIT II </t>
@@ -2974,7 +2974,7 @@
     <t>146_206</t>
   </si>
   <si>
-    <t>153_206</t>
+    <t>166_206</t>
   </si>
   <si>
     <t>139_207</t>
@@ -2983,12 +2983,12 @@
     <t>144_207</t>
   </si>
   <si>
+    <t>146_207</t>
+  </si>
+  <si>
     <t>153_207</t>
   </si>
   <si>
-    <t>166_207</t>
-  </si>
-  <si>
     <t>89_20</t>
   </si>
   <si>
@@ -3025,6 +3025,9 @@
     <t>149_232</t>
   </si>
   <si>
+    <t>150_232</t>
+  </si>
+  <si>
     <t>165_232</t>
   </si>
   <si>
@@ -3037,13 +3040,10 @@
     <t>138_233</t>
   </si>
   <si>
-    <t>147_233</t>
-  </si>
-  <si>
-    <t>150_233</t>
-  </si>
-  <si>
-    <t>135_234</t>
+    <t>165_233</t>
+  </si>
+  <si>
+    <t>165_234</t>
   </si>
   <si>
     <t>164_236</t>
@@ -3106,7 +3106,7 @@
     <t>154_250</t>
   </si>
   <si>
-    <t>154_251</t>
+    <t>141_251</t>
   </si>
   <si>
     <t>61_253</t>
@@ -3307,12 +3307,12 @@
     <t>102_327</t>
   </si>
   <si>
-    <t>101_329</t>
-  </si>
-  <si>
     <t>103_329</t>
   </si>
   <si>
+    <t>101_330</t>
+  </si>
+  <si>
     <t>103_330</t>
   </si>
   <si>
@@ -3511,18 +3511,18 @@
     <t>187_411</t>
   </si>
   <si>
-    <t>193_411</t>
+    <t>189_411</t>
   </si>
   <si>
     <t>195_411</t>
   </si>
   <si>
-    <t>189_412</t>
-  </si>
-  <si>
     <t>193_412</t>
   </si>
   <si>
+    <t>195_412</t>
+  </si>
+  <si>
     <t>186_415</t>
   </si>
   <si>
@@ -3643,7 +3643,7 @@
     <t>174_448</t>
   </si>
   <si>
-    <t>180_448</t>
+    <t>179_448</t>
   </si>
   <si>
     <t>182_448</t>
@@ -3994,7 +3994,7 @@
     <t>68_249</t>
   </si>
   <si>
-    <t>235_251</t>
+    <t>68_251</t>
   </si>
   <si>
     <t>73_251</t>
@@ -20039,7 +20039,7 @@
         <v>733</v>
       </c>
       <c r="R249">
-        <v>37740</v>
+        <v>22540</v>
       </c>
       <c r="S249" t="s">
         <v>984</v>
@@ -20080,7 +20080,7 @@
         <v>473</v>
       </c>
       <c r="K250">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="L250" t="s">
         <v>537</v>
@@ -20092,16 +20092,16 @@
         <v>32</v>
       </c>
       <c r="O250">
-        <v>29.54</v>
+        <v>29.56</v>
       </c>
       <c r="P250">
-        <v>74.31999999999999</v>
+        <v>74.39</v>
       </c>
       <c r="Q250" t="s">
         <v>733</v>
       </c>
       <c r="R250">
-        <v>45000</v>
+        <v>60200</v>
       </c>
       <c r="S250" t="s">
         <v>985</v>
@@ -20266,10 +20266,10 @@
         <v>473</v>
       </c>
       <c r="K253">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="L253" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="M253" t="s">
         <v>22</v>
@@ -20278,16 +20278,16 @@
         <v>32</v>
       </c>
       <c r="O253">
-        <v>29.54</v>
+        <v>29.56</v>
       </c>
       <c r="P253">
-        <v>74.31999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="Q253" t="s">
         <v>733</v>
       </c>
       <c r="R253">
-        <v>22200</v>
+        <v>15200</v>
       </c>
       <c r="S253" t="s">
         <v>988</v>
@@ -20328,7 +20328,7 @@
         <v>473</v>
       </c>
       <c r="K254">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="L254" t="s">
         <v>538</v>
@@ -20340,16 +20340,16 @@
         <v>32</v>
       </c>
       <c r="O254">
-        <v>29.56</v>
+        <v>29.54</v>
       </c>
       <c r="P254">
-        <v>74.39</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="Q254" t="s">
         <v>733</v>
       </c>
       <c r="R254">
-        <v>60200</v>
+        <v>67200</v>
       </c>
       <c r="S254" t="s">
         <v>989</v>
@@ -21031,7 +21031,7 @@
         <v>733</v>
       </c>
       <c r="R265">
-        <v>15665.5</v>
+        <v>59878</v>
       </c>
       <c r="S265" t="s">
         <v>1000</v>
@@ -21134,7 +21134,7 @@
         <v>473</v>
       </c>
       <c r="K267">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="L267" t="s">
         <v>545</v>
@@ -21146,16 +21146,16 @@
         <v>32</v>
       </c>
       <c r="O267">
-        <v>29.47</v>
+        <v>29.51</v>
       </c>
       <c r="P267">
-        <v>74.03</v>
+        <v>74.06</v>
       </c>
       <c r="Q267" t="s">
         <v>733</v>
       </c>
       <c r="R267">
-        <v>89574.5</v>
+        <v>43400</v>
       </c>
       <c r="S267" t="s">
         <v>1002</v>
@@ -21181,10 +21181,10 @@
         <v>32</v>
       </c>
       <c r="F268">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G268" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H268">
         <v>29.49</v>
@@ -21196,7 +21196,7 @@
         <v>473</v>
       </c>
       <c r="K268">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="L268" t="s">
         <v>546</v>
@@ -21208,16 +21208,16 @@
         <v>32</v>
       </c>
       <c r="O268">
-        <v>29.49</v>
+        <v>29.47</v>
       </c>
       <c r="P268">
-        <v>74.06999999999999</v>
+        <v>74.03</v>
       </c>
       <c r="Q268" t="s">
         <v>733</v>
       </c>
       <c r="R268">
-        <v>42647.5</v>
+        <v>1962</v>
       </c>
       <c r="S268" t="s">
         <v>1003</v>
@@ -21258,7 +21258,7 @@
         <v>473</v>
       </c>
       <c r="K269">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L269" t="s">
         <v>547</v>
@@ -21320,10 +21320,10 @@
         <v>473</v>
       </c>
       <c r="K270">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L270" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="M270" t="s">
         <v>22</v>
@@ -21332,16 +21332,16 @@
         <v>32</v>
       </c>
       <c r="O270">
-        <v>29.46</v>
+        <v>29.49</v>
       </c>
       <c r="P270">
-        <v>74.03</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="Q270" t="s">
         <v>733</v>
       </c>
       <c r="R270">
-        <v>128070</v>
+        <v>44800</v>
       </c>
       <c r="S270" t="s">
         <v>1005</v>
@@ -21382,10 +21382,10 @@
         <v>473</v>
       </c>
       <c r="K271">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="L271" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="M271" t="s">
         <v>22</v>
@@ -21394,16 +21394,16 @@
         <v>32</v>
       </c>
       <c r="O271">
-        <v>29.55</v>
+        <v>29.46</v>
       </c>
       <c r="P271">
-        <v>74.09</v>
+        <v>74.03</v>
       </c>
       <c r="Q271" t="s">
         <v>733</v>
       </c>
       <c r="R271">
-        <v>44212.5</v>
+        <v>128070</v>
       </c>
       <c r="S271" t="s">
         <v>1006</v>
@@ -21444,10 +21444,10 @@
         <v>473</v>
       </c>
       <c r="K272">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="L272" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="M272" t="s">
         <v>22</v>
@@ -21456,16 +21456,16 @@
         <v>32</v>
       </c>
       <c r="O272">
-        <v>29.51</v>
+        <v>29.47</v>
       </c>
       <c r="P272">
-        <v>74.06</v>
+        <v>74.03</v>
       </c>
       <c r="Q272" t="s">
         <v>733</v>
       </c>
       <c r="R272">
-        <v>43400</v>
+        <v>85460</v>
       </c>
       <c r="S272" t="s">
         <v>1007</v>
@@ -21506,7 +21506,7 @@
         <v>473</v>
       </c>
       <c r="K273">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="L273" t="s">
         <v>546</v>
@@ -21518,10 +21518,10 @@
         <v>32</v>
       </c>
       <c r="O273">
-        <v>29.49</v>
+        <v>29.47</v>
       </c>
       <c r="P273">
-        <v>74.06999999999999</v>
+        <v>74.03</v>
       </c>
       <c r="Q273" t="s">
         <v>733</v>
@@ -22643,7 +22643,7 @@
         <v>733</v>
       </c>
       <c r="R291">
-        <v>48820</v>
+        <v>17710</v>
       </c>
       <c r="S291" t="s">
         <v>1026</v>
@@ -22767,7 +22767,7 @@
         <v>733</v>
       </c>
       <c r="R293">
-        <v>36090</v>
+        <v>67200</v>
       </c>
       <c r="S293" t="s">
         <v>1028</v>
@@ -22808,10 +22808,10 @@
         <v>473</v>
       </c>
       <c r="K294">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="L294" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="M294" t="s">
         <v>22</v>
@@ -22820,10 +22820,10 @@
         <v>32</v>
       </c>
       <c r="O294">
-        <v>29.56</v>
+        <v>29.51</v>
       </c>
       <c r="P294">
-        <v>74.48999999999999</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="Q294" t="s">
         <v>733</v>
@@ -26962,10 +26962,10 @@
         <v>473</v>
       </c>
       <c r="K361">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L361" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="M361" t="s">
         <v>22</v>
@@ -26974,16 +26974,16 @@
         <v>42</v>
       </c>
       <c r="O361">
-        <v>25.14431</v>
+        <v>25.06257</v>
       </c>
       <c r="P361">
-        <v>75.8625</v>
+        <v>75.84820999999999</v>
       </c>
       <c r="Q361" t="s">
         <v>733</v>
       </c>
       <c r="R361">
-        <v>17390.2</v>
+        <v>28520</v>
       </c>
       <c r="S361" t="s">
         <v>1096</v>
@@ -27009,10 +27009,10 @@
         <v>42</v>
       </c>
       <c r="F362">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G362" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H362">
         <v>25.13</v>
@@ -27024,10 +27024,10 @@
         <v>473</v>
       </c>
       <c r="K362">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L362" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="M362" t="s">
         <v>22</v>
@@ -27036,16 +27036,16 @@
         <v>42</v>
       </c>
       <c r="O362">
-        <v>25.06257</v>
+        <v>25.14431</v>
       </c>
       <c r="P362">
-        <v>75.84820999999999</v>
+        <v>75.8625</v>
       </c>
       <c r="Q362" t="s">
         <v>733</v>
       </c>
       <c r="R362">
-        <v>11129.8</v>
+        <v>17390.2</v>
       </c>
       <c r="S362" t="s">
         <v>1097</v>
@@ -27107,7 +27107,7 @@
         <v>733</v>
       </c>
       <c r="R363">
-        <v>27390</v>
+        <v>9999.799999999999</v>
       </c>
       <c r="S363" t="s">
         <v>1098</v>
@@ -31178,7 +31178,7 @@
         <v>473</v>
       </c>
       <c r="K429">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L429" t="s">
         <v>612</v>
@@ -31190,16 +31190,16 @@
         <v>47</v>
       </c>
       <c r="O429">
-        <v>29.37</v>
+        <v>29.35</v>
       </c>
       <c r="P429">
-        <v>73.66</v>
+        <v>73.67</v>
       </c>
       <c r="Q429" t="s">
         <v>733</v>
       </c>
       <c r="R429">
-        <v>37010</v>
+        <v>64400</v>
       </c>
       <c r="S429" t="s">
         <v>1164</v>
@@ -31261,7 +31261,7 @@
         <v>733</v>
       </c>
       <c r="R430">
-        <v>64400</v>
+        <v>37010</v>
       </c>
       <c r="S430" t="s">
         <v>1165</v>
@@ -31302,7 +31302,7 @@
         <v>473</v>
       </c>
       <c r="K431">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L431" t="s">
         <v>614</v>
@@ -31314,16 +31314,16 @@
         <v>47</v>
       </c>
       <c r="O431">
-        <v>29.35</v>
+        <v>29.37</v>
       </c>
       <c r="P431">
-        <v>73.67</v>
+        <v>73.66</v>
       </c>
       <c r="Q431" t="s">
         <v>733</v>
       </c>
       <c r="R431">
-        <v>64400</v>
+        <v>44800</v>
       </c>
       <c r="S431" t="s">
         <v>1166</v>
@@ -31364,10 +31364,10 @@
         <v>473</v>
       </c>
       <c r="K432">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L432" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M432" t="s">
         <v>22</v>
@@ -31376,16 +31376,16 @@
         <v>47</v>
       </c>
       <c r="O432">
-        <v>29.37</v>
+        <v>29.34</v>
       </c>
       <c r="P432">
-        <v>73.66</v>
+        <v>73.67</v>
       </c>
       <c r="Q432" t="s">
         <v>733</v>
       </c>
       <c r="R432">
-        <v>7790</v>
+        <v>27390</v>
       </c>
       <c r="S432" t="s">
         <v>1167</v>
@@ -33906,7 +33906,7 @@
         <v>473</v>
       </c>
       <c r="K473">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L473" t="s">
         <v>638</v>
@@ -34033,7 +34033,7 @@
         <v>179</v>
       </c>
       <c r="L475" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="M475" t="s">
         <v>22</v>
@@ -34051,7 +34051,7 @@
         <v>733</v>
       </c>
       <c r="R475">
-        <v>33600</v>
+        <v>2920</v>
       </c>
       <c r="S475" t="s">
         <v>1210</v>
@@ -34095,7 +34095,7 @@
         <v>180</v>
       </c>
       <c r="L476" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M476" t="s">
         <v>22</v>
@@ -34113,7 +34113,7 @@
         <v>733</v>
       </c>
       <c r="R476">
-        <v>2920</v>
+        <v>33600</v>
       </c>
       <c r="S476" t="s">
         <v>1211</v>
@@ -41160,22 +41160,22 @@
         <v>473</v>
       </c>
       <c r="K590">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="L590" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="M590" t="s">
         <v>22</v>
       </c>
       <c r="N590" t="s">
-        <v>32</v>
+        <v>729</v>
       </c>
       <c r="O590">
-        <v>29.52</v>
+        <v>27.5</v>
       </c>
       <c r="P590">
-        <v>74.51000000000001</v>
+        <v>75.61</v>
       </c>
       <c r="Q590" t="s">
         <v>733</v>
@@ -41305,7 +41305,7 @@
         <v>733</v>
       </c>
       <c r="R592">
-        <v>14997</v>
+        <v>73400</v>
       </c>
       <c r="S592" t="s">
         <v>1327</v>
@@ -41491,7 +41491,7 @@
         <v>733</v>
       </c>
       <c r="R595">
-        <v>80470</v>
+        <v>22067</v>
       </c>
       <c r="S595" t="s">
         <v>1330</v>

--- a/pds_admin_raj/Backend/Backend/Result_Sheet12.xlsx
+++ b/pds_admin_raj/Backend/Backend/Result_Sheet12.xlsx
@@ -1629,12 +1629,12 @@
     <t>PWS NEELKANTH WAEHOUSE HMH</t>
   </si>
   <si>
+    <t>PWS PREETI ENTERPRISES HMO</t>
+  </si>
+  <si>
     <t>PWS ABP AGRIWAREHOUSING HMO</t>
   </si>
   <si>
-    <t>PWS PREETI ENTERPRISES HMO</t>
-  </si>
-  <si>
     <t xml:space="preserve">CWC BARAN </t>
   </si>
   <si>
@@ -1851,18 +1851,18 @@
     <t>PWS SUNIL SARAWAGI JAITSAR</t>
   </si>
   <si>
+    <t>PWS RAJ WAREHOUSING JAITSAR</t>
+  </si>
+  <si>
+    <t>PWS MRG WAREHOUSE JAITSAR</t>
+  </si>
+  <si>
+    <t>PWS MAMTA DEVI JAITSAR</t>
+  </si>
+  <si>
     <t>PWS REKHA DEVI JAITSAR</t>
   </si>
   <si>
-    <t>PWS RAJ WAREHOUSING JAITSAR</t>
-  </si>
-  <si>
-    <t>PWS MAMTA DEVI JAITSAR</t>
-  </si>
-  <si>
-    <t>PWS MRG WAREHOUSE JAITSAR</t>
-  </si>
-  <si>
     <t>PWS RELIABLE STATE SEEDS CORP KESRISINGHPUR</t>
   </si>
   <si>
@@ -1905,6 +1905,9 @@
     <t>PWS RAJ WAREHOUSING SBNR</t>
   </si>
   <si>
+    <t>PWS MALWA AGRO SBNR</t>
+  </si>
+  <si>
     <t>PWS MAJHA AGRO SBNR</t>
   </si>
   <si>
@@ -1923,22 +1926,19 @@
     <t>PWS ANITA GUPTA SRIKARANPUR</t>
   </si>
   <si>
-    <t>PWS MALWA AGRO SBNR</t>
-  </si>
-  <si>
     <t>PWS SUSHILA ENTERPRISES SURATGARH</t>
   </si>
   <si>
     <t>PWS SUSHILA ARORA SURATGARH</t>
   </si>
   <si>
+    <t>PWS SHAKTI GRAINRIES II SURATGARH</t>
+  </si>
+  <si>
+    <t>PWS SANKHLA ENTERPRISES SURATGARH</t>
+  </si>
+  <si>
     <t>PWS SHAKTI GRANARIES SURATGARH</t>
-  </si>
-  <si>
-    <t>PWS SANKHLA ENTERPRISES SURATGARH</t>
-  </si>
-  <si>
-    <t>PWS SHAKTI GRAINRIES II SURATGARH</t>
   </si>
   <si>
     <t xml:space="preserve">RSWC BUNDI HATTIPURA UNIT II </t>
@@ -2965,7 +2965,7 @@
     <t>155_203</t>
   </si>
   <si>
-    <t>161_203</t>
+    <t>160_203</t>
   </si>
   <si>
     <t>167_203</t>
@@ -2974,7 +2974,7 @@
     <t>146_206</t>
   </si>
   <si>
-    <t>166_206</t>
+    <t>153_206</t>
   </si>
   <si>
     <t>139_207</t>
@@ -2986,7 +2986,7 @@
     <t>146_207</t>
   </si>
   <si>
-    <t>153_207</t>
+    <t>166_207</t>
   </si>
   <si>
     <t>89_20</t>
@@ -3043,7 +3043,7 @@
     <t>165_233</t>
   </si>
   <si>
-    <t>165_234</t>
+    <t>136_234</t>
   </si>
   <si>
     <t>164_236</t>
@@ -3307,12 +3307,12 @@
     <t>102_327</t>
   </si>
   <si>
+    <t>101_329</t>
+  </si>
+  <si>
     <t>103_329</t>
   </si>
   <si>
-    <t>101_330</t>
-  </si>
-  <si>
     <t>103_330</t>
   </si>
   <si>
@@ -3508,21 +3508,21 @@
     <t>175_411</t>
   </si>
   <si>
-    <t>187_411</t>
-  </si>
-  <si>
     <t>189_411</t>
   </si>
   <si>
+    <t>193_411</t>
+  </si>
+  <si>
     <t>195_411</t>
   </si>
   <si>
+    <t>187_412</t>
+  </si>
+  <si>
     <t>193_412</t>
   </si>
   <si>
-    <t>195_412</t>
-  </si>
-  <si>
     <t>186_415</t>
   </si>
   <si>
@@ -3607,6 +3607,9 @@
     <t>188_440</t>
   </si>
   <si>
+    <t>196_440</t>
+  </si>
+  <si>
     <t>197_440</t>
   </si>
   <si>
@@ -3631,10 +3634,7 @@
     <t>205_443</t>
   </si>
   <si>
-    <t>196_444</t>
-  </si>
-  <si>
-    <t>197_444</t>
+    <t>188_444</t>
   </si>
   <si>
     <t>173_448</t>
@@ -3643,7 +3643,7 @@
     <t>174_448</t>
   </si>
   <si>
-    <t>179_448</t>
+    <t>180_448</t>
   </si>
   <si>
     <t>182_448</t>
@@ -19605,7 +19605,7 @@
         <v>733</v>
       </c>
       <c r="R242">
-        <v>71400</v>
+        <v>9060</v>
       </c>
       <c r="S242" t="s">
         <v>977</v>
@@ -19667,7 +19667,7 @@
         <v>733</v>
       </c>
       <c r="R243">
-        <v>117160</v>
+        <v>179500</v>
       </c>
       <c r="S243" t="s">
         <v>978</v>
@@ -19894,10 +19894,10 @@
         <v>473</v>
       </c>
       <c r="K247">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L247" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M247" t="s">
         <v>22</v>
@@ -20039,7 +20039,7 @@
         <v>733</v>
       </c>
       <c r="R249">
-        <v>22540</v>
+        <v>15540</v>
       </c>
       <c r="S249" t="s">
         <v>984</v>
@@ -20080,7 +20080,7 @@
         <v>473</v>
       </c>
       <c r="K250">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="L250" t="s">
         <v>537</v>
@@ -20092,16 +20092,16 @@
         <v>32</v>
       </c>
       <c r="O250">
-        <v>29.56</v>
+        <v>29.54</v>
       </c>
       <c r="P250">
-        <v>74.39</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="Q250" t="s">
         <v>733</v>
       </c>
       <c r="R250">
-        <v>60200</v>
+        <v>67200</v>
       </c>
       <c r="S250" t="s">
         <v>985</v>
@@ -20287,7 +20287,7 @@
         <v>733</v>
       </c>
       <c r="R253">
-        <v>15200</v>
+        <v>22200</v>
       </c>
       <c r="S253" t="s">
         <v>988</v>
@@ -20328,7 +20328,7 @@
         <v>473</v>
       </c>
       <c r="K254">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="L254" t="s">
         <v>538</v>
@@ -20340,16 +20340,16 @@
         <v>32</v>
       </c>
       <c r="O254">
-        <v>29.54</v>
+        <v>29.56</v>
       </c>
       <c r="P254">
-        <v>74.31999999999999</v>
+        <v>74.39</v>
       </c>
       <c r="Q254" t="s">
         <v>733</v>
       </c>
       <c r="R254">
-        <v>67200</v>
+        <v>60200</v>
       </c>
       <c r="S254" t="s">
         <v>989</v>
@@ -21341,7 +21341,7 @@
         <v>733</v>
       </c>
       <c r="R270">
-        <v>44800</v>
+        <v>42647.5</v>
       </c>
       <c r="S270" t="s">
         <v>1005</v>
@@ -21465,7 +21465,7 @@
         <v>733</v>
       </c>
       <c r="R272">
-        <v>85460</v>
+        <v>87612.5</v>
       </c>
       <c r="S272" t="s">
         <v>1007</v>
@@ -21506,10 +21506,10 @@
         <v>473</v>
       </c>
       <c r="K273">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="L273" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M273" t="s">
         <v>22</v>
@@ -21518,10 +21518,10 @@
         <v>32</v>
       </c>
       <c r="O273">
-        <v>29.47</v>
+        <v>29.49</v>
       </c>
       <c r="P273">
-        <v>74.03</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="Q273" t="s">
         <v>733</v>
@@ -26962,10 +26962,10 @@
         <v>473</v>
       </c>
       <c r="K361">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L361" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="M361" t="s">
         <v>22</v>
@@ -26974,16 +26974,16 @@
         <v>42</v>
       </c>
       <c r="O361">
-        <v>25.06257</v>
+        <v>25.14431</v>
       </c>
       <c r="P361">
-        <v>75.84820999999999</v>
+        <v>75.8625</v>
       </c>
       <c r="Q361" t="s">
         <v>733</v>
       </c>
       <c r="R361">
-        <v>28520</v>
+        <v>17390.2</v>
       </c>
       <c r="S361" t="s">
         <v>1096</v>
@@ -27009,10 +27009,10 @@
         <v>42</v>
       </c>
       <c r="F362">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G362" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H362">
         <v>25.13</v>
@@ -27024,10 +27024,10 @@
         <v>473</v>
       </c>
       <c r="K362">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L362" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="M362" t="s">
         <v>22</v>
@@ -27036,16 +27036,16 @@
         <v>42</v>
       </c>
       <c r="O362">
-        <v>25.14431</v>
+        <v>25.06257</v>
       </c>
       <c r="P362">
-        <v>75.8625</v>
+        <v>75.84820999999999</v>
       </c>
       <c r="Q362" t="s">
         <v>733</v>
       </c>
       <c r="R362">
-        <v>17390.2</v>
+        <v>11129.8</v>
       </c>
       <c r="S362" t="s">
         <v>1097</v>
@@ -27107,7 +27107,7 @@
         <v>733</v>
       </c>
       <c r="R363">
-        <v>9999.799999999999</v>
+        <v>27390</v>
       </c>
       <c r="S363" t="s">
         <v>1098</v>
@@ -31116,7 +31116,7 @@
         <v>473</v>
       </c>
       <c r="K428">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L428" t="s">
         <v>611</v>
@@ -31128,7 +31128,7 @@
         <v>47</v>
       </c>
       <c r="O428">
-        <v>29.34</v>
+        <v>29.35</v>
       </c>
       <c r="P428">
         <v>73.67</v>
@@ -31137,7 +31137,7 @@
         <v>733</v>
       </c>
       <c r="R428">
-        <v>36400</v>
+        <v>64400</v>
       </c>
       <c r="S428" t="s">
         <v>1163</v>
@@ -31178,7 +31178,7 @@
         <v>473</v>
       </c>
       <c r="K429">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L429" t="s">
         <v>612</v>
@@ -31190,16 +31190,16 @@
         <v>47</v>
       </c>
       <c r="O429">
-        <v>29.35</v>
+        <v>29.37</v>
       </c>
       <c r="P429">
-        <v>73.67</v>
+        <v>73.66</v>
       </c>
       <c r="Q429" t="s">
         <v>733</v>
       </c>
       <c r="R429">
-        <v>64400</v>
+        <v>9010</v>
       </c>
       <c r="S429" t="s">
         <v>1164</v>
@@ -31261,7 +31261,7 @@
         <v>733</v>
       </c>
       <c r="R430">
-        <v>37010</v>
+        <v>64400</v>
       </c>
       <c r="S430" t="s">
         <v>1165</v>
@@ -31302,7 +31302,7 @@
         <v>473</v>
       </c>
       <c r="K431">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L431" t="s">
         <v>614</v>
@@ -31314,16 +31314,16 @@
         <v>47</v>
       </c>
       <c r="O431">
-        <v>29.37</v>
+        <v>29.34</v>
       </c>
       <c r="P431">
-        <v>73.66</v>
+        <v>73.67</v>
       </c>
       <c r="Q431" t="s">
         <v>733</v>
       </c>
       <c r="R431">
-        <v>44800</v>
+        <v>36400</v>
       </c>
       <c r="S431" t="s">
         <v>1166</v>
@@ -31364,10 +31364,10 @@
         <v>473</v>
       </c>
       <c r="K432">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L432" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M432" t="s">
         <v>22</v>
@@ -31376,16 +31376,16 @@
         <v>47</v>
       </c>
       <c r="O432">
-        <v>29.34</v>
+        <v>29.37</v>
       </c>
       <c r="P432">
-        <v>73.67</v>
+        <v>73.66</v>
       </c>
       <c r="Q432" t="s">
         <v>733</v>
       </c>
       <c r="R432">
-        <v>27390</v>
+        <v>35790</v>
       </c>
       <c r="S432" t="s">
         <v>1167</v>
@@ -33121,7 +33121,7 @@
         <v>733</v>
       </c>
       <c r="R460">
-        <v>71700</v>
+        <v>5140</v>
       </c>
       <c r="S460" t="s">
         <v>1195</v>
@@ -33162,7 +33162,7 @@
         <v>473</v>
       </c>
       <c r="K461">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L461" t="s">
         <v>629</v>
@@ -33183,7 +33183,7 @@
         <v>733</v>
       </c>
       <c r="R461">
-        <v>56640</v>
+        <v>61600</v>
       </c>
       <c r="S461" t="s">
         <v>1196</v>
@@ -33209,22 +33209,22 @@
         <v>47</v>
       </c>
       <c r="F462">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G462" t="s">
-        <v>387</v>
+        <v>181</v>
       </c>
       <c r="H462">
-        <v>29.91</v>
+        <v>29.25</v>
       </c>
       <c r="I462">
-        <v>73.87</v>
+        <v>73.5</v>
       </c>
       <c r="J462" t="s">
         <v>473</v>
       </c>
       <c r="K462">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L462" t="s">
         <v>630</v>
@@ -33236,16 +33236,16 @@
         <v>47</v>
       </c>
       <c r="O462">
-        <v>29.85</v>
+        <v>29.31</v>
       </c>
       <c r="P462">
-        <v>73.87</v>
+        <v>73.5</v>
       </c>
       <c r="Q462" t="s">
         <v>733</v>
       </c>
       <c r="R462">
-        <v>74700</v>
+        <v>61600</v>
       </c>
       <c r="S462" t="s">
         <v>1197</v>
@@ -33286,7 +33286,7 @@
         <v>473</v>
       </c>
       <c r="K463">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L463" t="s">
         <v>631</v>
@@ -33298,16 +33298,16 @@
         <v>47</v>
       </c>
       <c r="O463">
-        <v>29.93</v>
+        <v>29.85</v>
       </c>
       <c r="P463">
-        <v>73.89</v>
+        <v>73.87</v>
       </c>
       <c r="Q463" t="s">
         <v>733</v>
       </c>
       <c r="R463">
-        <v>144014.5</v>
+        <v>74700</v>
       </c>
       <c r="S463" t="s">
         <v>1198</v>
@@ -33348,10 +33348,10 @@
         <v>473</v>
       </c>
       <c r="K464">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L464" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="M464" t="s">
         <v>22</v>
@@ -33360,16 +33360,16 @@
         <v>47</v>
       </c>
       <c r="O464">
-        <v>29.84</v>
+        <v>29.93</v>
       </c>
       <c r="P464">
-        <v>73.88</v>
+        <v>73.89</v>
       </c>
       <c r="Q464" t="s">
         <v>733</v>
       </c>
       <c r="R464">
-        <v>51285.5</v>
+        <v>144014.5</v>
       </c>
       <c r="S464" t="s">
         <v>1199</v>
@@ -33395,10 +33395,10 @@
         <v>47</v>
       </c>
       <c r="F465">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G465" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H465">
         <v>29.91</v>
@@ -33410,10 +33410,10 @@
         <v>473</v>
       </c>
       <c r="K465">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="L465" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="M465" t="s">
         <v>22</v>
@@ -33422,16 +33422,16 @@
         <v>47</v>
       </c>
       <c r="O465">
-        <v>29.85</v>
+        <v>29.84</v>
       </c>
       <c r="P465">
-        <v>73.87</v>
+        <v>73.88</v>
       </c>
       <c r="Q465" t="s">
         <v>733</v>
       </c>
       <c r="R465">
-        <v>88500</v>
+        <v>51285.5</v>
       </c>
       <c r="S465" t="s">
         <v>1200</v>
@@ -33472,10 +33472,10 @@
         <v>473</v>
       </c>
       <c r="K466">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="L466" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="M466" t="s">
         <v>22</v>
@@ -33484,16 +33484,16 @@
         <v>47</v>
       </c>
       <c r="O466">
-        <v>29.84</v>
+        <v>29.85</v>
       </c>
       <c r="P466">
-        <v>73.88</v>
+        <v>73.87</v>
       </c>
       <c r="Q466" t="s">
         <v>733</v>
       </c>
       <c r="R466">
-        <v>33684.5</v>
+        <v>88500</v>
       </c>
       <c r="S466" t="s">
         <v>1201</v>
@@ -33519,25 +33519,25 @@
         <v>47</v>
       </c>
       <c r="F467">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G467" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H467">
-        <v>29.84</v>
+        <v>29.91</v>
       </c>
       <c r="I467">
-        <v>73.45999999999999</v>
+        <v>73.87</v>
       </c>
       <c r="J467" t="s">
         <v>473</v>
       </c>
       <c r="K467">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L467" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="M467" t="s">
         <v>22</v>
@@ -33549,13 +33549,13 @@
         <v>29.84</v>
       </c>
       <c r="P467">
-        <v>73.48</v>
+        <v>73.88</v>
       </c>
       <c r="Q467" t="s">
         <v>733</v>
       </c>
       <c r="R467">
-        <v>81500</v>
+        <v>33684.5</v>
       </c>
       <c r="S467" t="s">
         <v>1202</v>
@@ -33596,7 +33596,7 @@
         <v>473</v>
       </c>
       <c r="K468">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="L468" t="s">
         <v>634</v>
@@ -33611,13 +33611,13 @@
         <v>29.84</v>
       </c>
       <c r="P468">
-        <v>73.48999999999999</v>
+        <v>73.48</v>
       </c>
       <c r="Q468" t="s">
         <v>733</v>
       </c>
       <c r="R468">
-        <v>40300</v>
+        <v>81500</v>
       </c>
       <c r="S468" t="s">
         <v>1203</v>
@@ -33643,22 +33643,22 @@
         <v>47</v>
       </c>
       <c r="F469">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H469">
-        <v>29.25</v>
+        <v>29.84</v>
       </c>
       <c r="I469">
-        <v>73.5</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="J469" t="s">
         <v>473</v>
       </c>
       <c r="K469">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="L469" t="s">
         <v>635</v>
@@ -33670,16 +33670,16 @@
         <v>47</v>
       </c>
       <c r="O469">
-        <v>29.31</v>
+        <v>29.84</v>
       </c>
       <c r="P469">
-        <v>73.5</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="Q469" t="s">
         <v>733</v>
       </c>
       <c r="R469">
-        <v>61600</v>
+        <v>40300</v>
       </c>
       <c r="S469" t="s">
         <v>1204</v>
@@ -33720,10 +33720,10 @@
         <v>473</v>
       </c>
       <c r="K470">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="L470" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="M470" t="s">
         <v>22</v>
@@ -33732,7 +33732,7 @@
         <v>47</v>
       </c>
       <c r="O470">
-        <v>29.31</v>
+        <v>29.24</v>
       </c>
       <c r="P470">
         <v>73.5</v>
@@ -33741,7 +33741,7 @@
         <v>733</v>
       </c>
       <c r="R470">
-        <v>4960</v>
+        <v>66560</v>
       </c>
       <c r="S470" t="s">
         <v>1205</v>
@@ -33906,7 +33906,7 @@
         <v>473</v>
       </c>
       <c r="K473">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L473" t="s">
         <v>638</v>
@@ -34033,7 +34033,7 @@
         <v>179</v>
       </c>
       <c r="L475" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M475" t="s">
         <v>22</v>
@@ -34051,7 +34051,7 @@
         <v>733</v>
       </c>
       <c r="R475">
-        <v>2920</v>
+        <v>33600</v>
       </c>
       <c r="S475" t="s">
         <v>1210</v>
@@ -34095,7 +34095,7 @@
         <v>180</v>
       </c>
       <c r="L476" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="M476" t="s">
         <v>22</v>
@@ -34113,7 +34113,7 @@
         <v>733</v>
       </c>
       <c r="R476">
-        <v>33600</v>
+        <v>2920</v>
       </c>
       <c r="S476" t="s">
         <v>1211</v>
